--- a/src/assets/files/dkVstep/mau-imoport-duthi-tram.xlsx
+++ b/src/assets/files/dkVstep/mau-imoport-duthi-tram.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data\project\angular\v14\dangky-vstep\src\assets\files\dkVstep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ABC0F9-F7DB-4E95-B8D2-0677DCD2D03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1831929-BDB4-463C-A8B4-E6484570B9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
   <si>
     <t>Địa chỉ email</t>
   </si>
@@ -147,13 +147,22 @@
   </si>
   <si>
     <t>Nữ</t>
+  </si>
+  <si>
+    <t>15/05/2002</t>
+  </si>
+  <si>
+    <t>15/12/2003</t>
+  </si>
+  <si>
+    <t>05/05/2004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -189,6 +198,11 @@
       <sz val="10"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -327,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -406,12 +420,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="26">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -430,21 +468,39 @@
       </font>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -698,51 +754,6 @@
       <font>
         <color theme="1"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="mm/dd/yy"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -968,21 +979,21 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="17"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Trình độ đăng ký" dataDxfId="16"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Họ, tên đệm " dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tên" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ngày sinh" dataDxfId="13"/>
-    <tableColumn id="13" xr3:uid="{8BD2DD4A-8DB1-4E46-842E-04C60F0C7E61}" name="Dân tộc" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Giới tính" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nơi sinh (chỉ ghi tên tỉnh, sau sáp nhập_x000a_ - ví dụ: Thái Nguyên)" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Số CCCD/Hộ chiếu" dataDxfId="10"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Anh CCCD mặt trước" dataDxfId="9"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Anh CCCD mặt sau" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Số điện thoại liên hệ" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Địa chỉ email" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Địa chỉ học tập/công tác/liên hệ" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Vui lòng tải lên ảnh thẻ (dạng ảnh thẻ, nền trắng hoặc xanh, áo có cổ)" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Vui lòng chọn hình thức nộp lệ phí thi" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ngày nộp lệ phí thi" dataDxfId="2"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vui lòng tải lên minh chứng nộp lệ phí thi tại đây" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Tên" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Ngày sinh" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{8BD2DD4A-8DB1-4E46-842E-04C60F0C7E61}" name="Dân tộc" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Giới tính" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nơi sinh (chỉ ghi tên tỉnh, sau sáp nhập_x000a_ - ví dụ: Thái Nguyên)" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Số CCCD/Hộ chiếu" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Anh CCCD mặt trước" dataDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Anh CCCD mặt sau" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Số điện thoại liên hệ" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Địa chỉ email" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Địa chỉ học tập/công tác/liên hệ" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Vui lòng tải lên ảnh thẻ (dạng ảnh thẻ, nền trắng hoặc xanh, áo có cổ)" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Vui lòng chọn hình thức nộp lệ phí thi" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Ngày nộp lệ phí thi" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Vui lòng tải lên minh chứng nộp lệ phí thi tại đây" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="Câu trả lời biểu mẫu 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1280,8 +1291,8 @@
       <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="2">
-        <v>37395</v>
+      <c r="E2" s="27" t="s">
+        <v>42</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
@@ -1326,8 +1337,8 @@
       <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="2">
-        <v>37129</v>
+      <c r="E3" s="27" t="s">
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>20</v>
@@ -1372,8 +1383,8 @@
       <c r="D4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="6">
-        <v>36469</v>
+      <c r="E4" s="27" t="s">
+        <v>44</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>32</v>
@@ -1406,6 +1417,7 @@
       <c r="T4" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
